--- a/SIMPLE TOY EXAMPLE ppm_output_handcalc.xlsx
+++ b/SIMPLE TOY EXAMPLE ppm_output_handcalc.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/enoch/Documents/Local Erill Research/drippy/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{777EAB0E-8BDF-F949-A028-5DA688AF3B67}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2A00AFFF-128A-6A48-A675-A67E94F4A4D8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="760" windowWidth="29400" windowHeight="18360" activeTab="2" xr2:uid="{BF39720B-7314-BE4F-87DC-079655431D8B}"/>
+    <workbookView xWindow="0" yWindow="760" windowWidth="29400" windowHeight="18360" xr2:uid="{BF39720B-7314-BE4F-87DC-079655431D8B}"/>
     <workbookView xWindow="0" yWindow="760" windowWidth="29400" windowHeight="18360" activeTab="3" xr2:uid="{4F083981-888D-6D4A-9A91-0CE6B4D6ABC5}"/>
   </bookViews>
   <sheets>
@@ -247,7 +247,7 @@
       <name val="Calibri (Body)"/>
     </font>
   </fonts>
-  <fills count="11">
+  <fills count="13">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -308,6 +308,18 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="3">
     <border>
@@ -345,7 +357,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="28">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
@@ -361,9 +373,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -387,6 +396,12 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="10" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2386,7 +2401,7 @@
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <sheetData>
     <row r="1" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="B1" s="8">
+      <c r="B1" s="24">
         <v>0</v>
       </c>
       <c r="C1" s="1">
@@ -2436,10 +2451,10 @@
       <c r="D2">
         <v>0</v>
       </c>
-      <c r="E2">
+      <c r="E2" s="26">
         <v>1</v>
       </c>
-      <c r="F2">
+      <c r="F2" s="27">
         <v>0.90625</v>
       </c>
       <c r="G2">
@@ -2457,7 +2472,7 @@
       <c r="K2">
         <v>1.5625E-2</v>
       </c>
-      <c r="L2">
+      <c r="L2" s="26">
         <v>1</v>
       </c>
       <c r="M2">
@@ -2474,7 +2489,7 @@
       <c r="C3">
         <v>1.5625E-2</v>
       </c>
-      <c r="D3">
+      <c r="D3" s="25">
         <v>0.984375</v>
       </c>
       <c r="E3">
@@ -2495,7 +2510,7 @@
       <c r="J3">
         <v>0</v>
       </c>
-      <c r="K3">
+      <c r="K3" s="25">
         <v>0.984375</v>
       </c>
       <c r="L3">
@@ -2509,7 +2524,7 @@
       <c r="A4" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="B4">
+      <c r="B4" s="25">
         <v>0.71875</v>
       </c>
       <c r="C4">
@@ -2524,13 +2539,13 @@
       <c r="F4">
         <v>0</v>
       </c>
-      <c r="G4">
+      <c r="G4" s="25">
         <v>0.59375</v>
       </c>
       <c r="H4">
         <v>0</v>
       </c>
-      <c r="I4">
+      <c r="I4" s="25">
         <v>0.734375</v>
       </c>
       <c r="J4">
@@ -2553,7 +2568,7 @@
       <c r="B5">
         <v>0</v>
       </c>
-      <c r="C5">
+      <c r="C5" s="26">
         <v>0.9375</v>
       </c>
       <c r="D5">
@@ -2568,13 +2583,13 @@
       <c r="G5">
         <v>0.15625</v>
       </c>
-      <c r="H5">
+      <c r="H5" s="26">
         <v>1</v>
       </c>
       <c r="I5">
         <v>0</v>
       </c>
-      <c r="J5">
+      <c r="J5" s="26">
         <v>0.984375</v>
       </c>
       <c r="K5">
@@ -2583,7 +2598,7 @@
       <c r="L5">
         <v>0</v>
       </c>
-      <c r="M5">
+      <c r="M5" s="26">
         <v>0.765625</v>
       </c>
     </row>
@@ -2616,46 +2631,46 @@
       <c r="A1" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="B1" s="15">
-        <v>0</v>
-      </c>
-      <c r="C1" s="15">
+      <c r="B1" s="14">
+        <v>0</v>
+      </c>
+      <c r="C1" s="14">
         <v>1</v>
       </c>
-      <c r="D1" s="15">
+      <c r="D1" s="14">
         <v>2</v>
       </c>
-      <c r="E1" s="15">
+      <c r="E1" s="14">
         <v>3</v>
       </c>
-      <c r="F1" s="15">
+      <c r="F1" s="14">
         <v>4</v>
       </c>
-      <c r="G1" s="15">
+      <c r="G1" s="14">
         <v>5</v>
       </c>
-      <c r="H1" s="15">
+      <c r="H1" s="14">
         <v>6</v>
       </c>
-      <c r="I1" s="15">
+      <c r="I1" s="14">
         <v>7</v>
       </c>
-      <c r="J1" s="15">
+      <c r="J1" s="14">
         <v>8</v>
       </c>
-      <c r="K1" s="15">
+      <c r="K1" s="14">
         <v>9</v>
       </c>
-      <c r="L1" s="15">
+      <c r="L1" s="14">
         <v>10</v>
       </c>
-      <c r="M1" s="15">
+      <c r="M1" s="14">
         <v>11</v>
       </c>
-      <c r="P1" s="17">
-        <v>0</v>
-      </c>
-      <c r="Q1" s="18">
+      <c r="P1" s="16">
+        <v>0</v>
+      </c>
+      <c r="Q1" s="17">
         <v>9</v>
       </c>
       <c r="R1" s="6" t="s">
@@ -2667,14 +2682,14 @@
       <c r="T1" s="7"/>
     </row>
     <row r="2" spans="1:20" x14ac:dyDescent="0.2">
-      <c r="A2" s="16">
+      <c r="A2" s="15">
         <v>0</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="5">
         <v>31.020705939999999</v>
       </c>
-      <c r="D2" s="20">
+      <c r="D2" s="19">
         <v>1.8600792660000001</v>
       </c>
       <c r="E2">
@@ -2689,19 +2704,19 @@
       <c r="H2">
         <v>33.219280939999997</v>
       </c>
-      <c r="I2" s="20">
+      <c r="I2" s="19">
         <v>7.1603760000000004E-3</v>
       </c>
       <c r="J2">
         <v>32.66223961</v>
       </c>
-      <c r="K2" s="20">
+      <c r="K2" s="19">
         <v>1.9307599209999999</v>
       </c>
       <c r="L2">
         <v>4.9999999900000001</v>
       </c>
-      <c r="M2" s="10">
+      <c r="M2" s="9">
         <v>25.116701679999998</v>
       </c>
       <c r="O2" s="3" t="s">
@@ -2725,7 +2740,7 @@
       </c>
     </row>
     <row r="3" spans="1:20" x14ac:dyDescent="0.2">
-      <c r="A3" s="16">
+      <c r="A3" s="15">
         <v>1</v>
       </c>
       <c r="B3" s="5">
@@ -2744,13 +2759,13 @@
       <c r="G3">
         <v>19.486305897411111</v>
       </c>
-      <c r="H3" s="20">
+      <c r="H3" s="19">
         <v>9.3109404381863367E-2</v>
       </c>
       <c r="I3">
         <v>25.043545593782468</v>
       </c>
-      <c r="J3" s="20">
+      <c r="J3" s="19">
         <v>4.4524455658293112E-2</v>
       </c>
       <c r="K3">
@@ -2759,7 +2774,7 @@
       <c r="L3">
         <v>4.4150374963453638</v>
       </c>
-      <c r="M3" s="20">
+      <c r="M3" s="19">
         <v>0.69197659349035723</v>
       </c>
       <c r="O3" s="3" t="s">
@@ -2783,7 +2798,7 @@
       </c>
     </row>
     <row r="4" spans="1:20" x14ac:dyDescent="0.2">
-      <c r="A4" s="16">
+      <c r="A4" s="15">
         <v>2</v>
       </c>
       <c r="B4" s="5">
@@ -2813,7 +2828,7 @@
       <c r="J4">
         <v>33.1031658738574</v>
       </c>
-      <c r="K4" s="20">
+      <c r="K4" s="19">
         <v>0.42530126497041992</v>
       </c>
       <c r="L4">
@@ -2843,7 +2858,7 @@
       </c>
     </row>
     <row r="5" spans="1:20" x14ac:dyDescent="0.2">
-      <c r="A5" s="16">
+      <c r="A5" s="15">
         <v>3</v>
       </c>
       <c r="B5" s="5">
@@ -2876,7 +2891,7 @@
       <c r="K5">
         <v>32.584114609028987</v>
       </c>
-      <c r="L5" s="20">
+      <c r="L5" s="19">
         <v>0</v>
       </c>
       <c r="M5">
@@ -2903,7 +2918,7 @@
       </c>
     </row>
     <row r="6" spans="1:20" x14ac:dyDescent="0.2">
-      <c r="A6" s="16">
+      <c r="A6" s="15">
         <v>4</v>
       </c>
       <c r="B6" s="5">
@@ -2915,7 +2930,7 @@
       <c r="D6">
         <v>33.1031658738574</v>
       </c>
-      <c r="E6" s="20">
+      <c r="E6" s="19">
         <v>0.1420190048575036</v>
       </c>
       <c r="F6" s="2">
@@ -2936,7 +2951,7 @@
       <c r="K6">
         <v>32.586333655979892</v>
       </c>
-      <c r="L6" s="20">
+      <c r="L6" s="19">
         <v>0.1420190048575036</v>
       </c>
       <c r="M6">
@@ -2956,10 +2971,10 @@
       </c>
     </row>
     <row r="7" spans="1:20" x14ac:dyDescent="0.2">
-      <c r="A7" s="16">
+      <c r="A7" s="15">
         <v>5</v>
       </c>
-      <c r="B7" s="19">
+      <c r="B7" s="18">
         <v>0.318100151</v>
       </c>
       <c r="C7">
@@ -2971,7 +2986,7 @@
       <c r="E7">
         <v>3.415037497884239</v>
       </c>
-      <c r="F7" s="20">
+      <c r="F7" s="19">
         <v>2.8970824849101051</v>
       </c>
       <c r="G7" s="2">
@@ -2980,7 +2995,7 @@
       <c r="H7">
         <v>2.6780719043335819</v>
       </c>
-      <c r="I7" s="20">
+      <c r="I7" s="19">
         <v>0.35433235746951702</v>
       </c>
       <c r="J7">
@@ -2992,18 +3007,18 @@
       <c r="L7">
         <v>3.415037497884239</v>
       </c>
-      <c r="M7" s="20">
+      <c r="M7" s="19">
         <v>1.892511612224304</v>
       </c>
     </row>
     <row r="8" spans="1:20" x14ac:dyDescent="0.2">
-      <c r="A8" s="16">
+      <c r="A8" s="15">
         <v>6</v>
       </c>
       <c r="B8" s="5">
         <v>32.220591110000001</v>
       </c>
-      <c r="C8" s="20">
+      <c r="C8" s="19">
         <v>1.688210110206448</v>
       </c>
       <c r="D8">
@@ -3024,7 +3039,7 @@
       <c r="I8">
         <v>32.298432137257187</v>
       </c>
-      <c r="J8" s="20">
+      <c r="J8" s="19">
         <v>0.4029361896679044</v>
       </c>
       <c r="K8">
@@ -3038,16 +3053,16 @@
       </c>
     </row>
     <row r="9" spans="1:20" x14ac:dyDescent="0.2">
-      <c r="A9" s="16">
+      <c r="A9" s="15">
         <v>7</v>
       </c>
-      <c r="B9" s="19">
+      <c r="B9" s="18">
         <v>8.9494190000000001E-3</v>
       </c>
       <c r="C9">
         <v>31.067580940164301</v>
       </c>
-      <c r="D9" s="20">
+      <c r="D9" s="19">
         <v>1.859594473605175</v>
       </c>
       <c r="E9">
@@ -3068,7 +3083,7 @@
       <c r="J9">
         <v>32.677864608886978</v>
       </c>
-      <c r="K9" s="20">
+      <c r="K9" s="19">
         <v>1.9463849242714379</v>
       </c>
       <c r="L9">
@@ -3079,13 +3094,13 @@
       </c>
     </row>
     <row r="10" spans="1:20" x14ac:dyDescent="0.2">
-      <c r="A10" s="16">
+      <c r="A10" s="15">
         <v>8</v>
       </c>
       <c r="B10" s="5">
         <v>31.369988580000001</v>
       </c>
-      <c r="C10" s="20">
+      <c r="C10" s="19">
         <v>0.43360638701186949</v>
       </c>
       <c r="D10">
@@ -3100,7 +3115,7 @@
       <c r="G10">
         <v>23.876910448498951</v>
       </c>
-      <c r="H10" s="20">
+      <c r="H10" s="19">
         <v>2.2720076497793468E-2</v>
       </c>
       <c r="I10">
@@ -3120,7 +3135,7 @@
       </c>
     </row>
     <row r="11" spans="1:20" x14ac:dyDescent="0.2">
-      <c r="A11" s="16">
+      <c r="A11" s="15">
         <v>9</v>
       </c>
       <c r="B11" s="5">
@@ -3129,7 +3144,7 @@
       <c r="C11">
         <v>31.03668594136634</v>
       </c>
-      <c r="D11" s="20">
+      <c r="D11" s="19">
         <v>0.42530126497041992</v>
       </c>
       <c r="E11">
@@ -3161,7 +3176,7 @@
       </c>
     </row>
     <row r="12" spans="1:20" x14ac:dyDescent="0.2">
-      <c r="A12" s="16">
+      <c r="A12" s="15">
         <v>10</v>
       </c>
       <c r="B12" s="5">
@@ -3173,7 +3188,7 @@
       <c r="D12">
         <v>33.1031658738574</v>
       </c>
-      <c r="E12" s="20">
+      <c r="E12" s="19">
         <v>0</v>
       </c>
       <c r="F12">
@@ -3202,13 +3217,13 @@
       </c>
     </row>
     <row r="13" spans="1:20" x14ac:dyDescent="0.2">
-      <c r="A13" s="16">
+      <c r="A13" s="15">
         <v>11</v>
       </c>
       <c r="B13" s="5">
         <v>24.43904822</v>
       </c>
-      <c r="C13" s="20">
+      <c r="C13" s="19">
         <v>1.5630732009148851</v>
       </c>
       <c r="D13">
@@ -3307,19 +3322,19 @@
       <c r="M1" s="1">
         <v>11</v>
       </c>
-      <c r="P1" s="9">
+      <c r="P1" s="8">
         <v>3</v>
       </c>
-      <c r="Q1" s="9">
+      <c r="Q1" s="8">
         <v>9</v>
       </c>
       <c r="R1" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="S1" s="22" t="s">
+      <c r="S1" s="21" t="s">
         <v>25</v>
       </c>
-      <c r="T1" s="22" t="s">
+      <c r="T1" s="21" t="s">
         <v>26</v>
       </c>
       <c r="U1" s="6" t="s">
@@ -3353,19 +3368,19 @@
       <c r="H2">
         <v>0.500655077</v>
       </c>
-      <c r="I2" s="12">
+      <c r="I2" s="11">
         <v>1.0382551289999999</v>
       </c>
       <c r="J2">
         <v>0.46412009799999998</v>
       </c>
-      <c r="K2" s="13">
+      <c r="K2" s="12">
         <v>0.91279231299999997</v>
       </c>
       <c r="L2">
         <v>0.60167079199999995</v>
       </c>
-      <c r="M2" s="10">
+      <c r="M2" s="9">
         <v>0.34988060900000001</v>
       </c>
       <c r="O2" s="3" t="s">
@@ -3417,13 +3432,13 @@
       <c r="G3" s="5">
         <v>0.43011038600000001</v>
       </c>
-      <c r="H3" s="13">
+      <c r="H3" s="12">
         <v>1.7740252299999999</v>
       </c>
       <c r="I3">
         <v>0.41379671899999998</v>
       </c>
-      <c r="J3" s="12">
+      <c r="J3" s="11">
         <v>1.7338225279999999</v>
       </c>
       <c r="K3">
@@ -3432,7 +3447,7 @@
       <c r="L3">
         <v>0.944073524</v>
       </c>
-      <c r="M3" s="13">
+      <c r="M3" s="12">
         <v>1.300679519</v>
       </c>
       <c r="O3" s="3" t="s">
@@ -3494,7 +3509,7 @@
       <c r="J4">
         <v>0.88388492366776417</v>
       </c>
-      <c r="K4" s="12">
+      <c r="K4" s="11">
         <v>1.8682599204038386</v>
       </c>
       <c r="L4">
@@ -3548,7 +3563,7 @@
         <v>0.94194245855622349</v>
       </c>
       <c r="E5" s="2"/>
-      <c r="F5" s="13">
+      <c r="F5" s="12">
         <v>1.7270291352821832</v>
       </c>
       <c r="G5">
@@ -3566,7 +3581,7 @@
       <c r="K5">
         <v>1.0001761108457747</v>
       </c>
-      <c r="L5" s="12">
+      <c r="L5" s="11">
         <v>1.9999999901784853</v>
       </c>
       <c r="M5">
@@ -3636,7 +3651,7 @@
       <c r="K6">
         <v>0.77464335699999998</v>
       </c>
-      <c r="L6" s="13">
+      <c r="L6" s="12">
         <v>1.727029135</v>
       </c>
       <c r="M6">
@@ -3658,7 +3673,7 @@
         <f>-SUM(U2:U5)</f>
         <v>0.99982388915422526</v>
       </c>
-      <c r="V6" s="11">
+      <c r="V6" s="10">
         <f xml:space="preserve"> 2 - U6</f>
         <v>1.0001761108457747</v>
       </c>
@@ -3739,7 +3754,7 @@
       <c r="I8">
         <v>0.53957559300000002</v>
       </c>
-      <c r="J8" s="13">
+      <c r="J8" s="12">
         <v>1.9340855809999999</v>
       </c>
       <c r="K8">
@@ -3748,7 +3763,7 @@
       <c r="L8">
         <v>0.99999999299999998</v>
       </c>
-      <c r="M8" s="13">
+      <c r="M8" s="12">
         <v>1.4787779750000001</v>
       </c>
     </row>
@@ -3788,7 +3803,7 @@
       <c r="J9">
         <v>0.49714305600000003</v>
       </c>
-      <c r="K9" s="13">
+      <c r="K9" s="12">
         <v>0.94581527099999996</v>
       </c>
       <c r="L9">
@@ -3841,7 +3856,7 @@
       <c r="L10">
         <v>1.000176111</v>
       </c>
-      <c r="M10" s="13">
+      <c r="M10" s="12">
         <v>1.414274295</v>
       </c>
     </row>
@@ -3993,7 +4008,7 @@
       <c r="M13" s="2"/>
     </row>
     <row r="16" spans="1:22" ht="32" x14ac:dyDescent="0.2">
-      <c r="A16" s="14" t="s">
+      <c r="A16" s="13" t="s">
         <v>10</v>
       </c>
       <c r="B16" t="s">
@@ -4005,7 +4020,7 @@
       <c r="D16" t="s">
         <v>9</v>
       </c>
-      <c r="L16" s="23"/>
+      <c r="L16" s="22"/>
     </row>
     <row r="17" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
@@ -4020,7 +4035,7 @@
       <c r="D17" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="L17" s="23"/>
+      <c r="L17" s="22"/>
     </row>
     <row r="18" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
@@ -4173,10 +4188,10 @@
       <c r="M1" s="1">
         <v>11</v>
       </c>
-      <c r="P1" s="9">
+      <c r="P1" s="8">
         <v>3</v>
       </c>
-      <c r="Q1" s="9">
+      <c r="Q1" s="8">
         <v>9</v>
       </c>
       <c r="R1" s="6" t="s">
@@ -4202,25 +4217,25 @@
       <c r="F2">
         <v>-0.50661061399999996</v>
       </c>
-      <c r="G2" s="12">
+      <c r="G2" s="11">
         <v>0.95141007099999997</v>
       </c>
       <c r="H2">
         <v>-0.50245943400000004</v>
       </c>
-      <c r="I2" s="21">
+      <c r="I2" s="20">
         <v>0.99980301599999999</v>
       </c>
       <c r="J2">
         <v>-0.51208986300000003</v>
       </c>
-      <c r="K2" s="24">
+      <c r="K2" s="23">
         <v>-7.01493E-3</v>
       </c>
       <c r="L2">
         <v>-0.43965200500000001</v>
       </c>
-      <c r="M2" s="10">
+      <c r="M2" s="9">
         <v>-0.53271688299999997</v>
       </c>
       <c r="O2" s="3" t="s">
@@ -4257,13 +4272,13 @@
       <c r="G3">
         <v>-0.30403879734200751</v>
       </c>
-      <c r="H3" s="12">
+      <c r="H3" s="11">
         <v>0.99909729815891835</v>
       </c>
       <c r="I3">
         <v>-0.52043820617740066</v>
       </c>
-      <c r="J3" s="12">
+      <c r="J3" s="11">
         <v>0.99958808090207341</v>
       </c>
       <c r="K3">
@@ -4272,7 +4287,7 @@
       <c r="L3">
         <v>-0.29518783809240762</v>
       </c>
-      <c r="M3" s="12">
+      <c r="M3" s="11">
         <v>0.94871716359144431</v>
       </c>
       <c r="O3" s="3" t="s">
@@ -4319,7 +4334,7 @@
       <c r="J4">
         <v>-0.34758995247793623</v>
       </c>
-      <c r="K4" s="12">
+      <c r="K4" s="11">
         <v>0.99966055668703313</v>
       </c>
       <c r="L4">
@@ -4358,7 +4373,7 @@
         <v>-0.34038701134538812</v>
       </c>
       <c r="E5" s="2"/>
-      <c r="F5" s="12">
+      <c r="F5" s="11">
         <v>0.99493667632618188</v>
       </c>
       <c r="G5">
@@ -4376,7 +4391,7 @@
       <c r="K5">
         <v>-0.31911282313630129</v>
       </c>
-      <c r="L5" s="12">
+      <c r="L5" s="11">
         <v>0.99999999999999944</v>
       </c>
       <c r="M5">
@@ -4431,7 +4446,7 @@
       <c r="K6">
         <v>-0.36512160936794091</v>
       </c>
-      <c r="L6" s="12">
+      <c r="L6" s="11">
         <v>0.99493667632618188</v>
       </c>
       <c r="M6">
@@ -4471,7 +4486,7 @@
       <c r="H7">
         <v>-0.27050089040022968</v>
       </c>
-      <c r="I7" s="12">
+      <c r="I7" s="11">
         <v>0.95414290742954877</v>
       </c>
       <c r="J7">
@@ -4519,7 +4534,7 @@
       <c r="I8">
         <v>-0.48652674699673709</v>
       </c>
-      <c r="J8" s="12">
+      <c r="J8" s="11">
         <v>0.99988684582707787</v>
       </c>
       <c r="K8">
@@ -4528,7 +4543,7 @@
       <c r="L8">
         <v>-0.33333333333333331</v>
       </c>
-      <c r="M8" s="12">
+      <c r="M8" s="11">
         <v>0.95203310929741403</v>
       </c>
     </row>
@@ -4621,7 +4636,7 @@
       <c r="L10">
         <v>-0.31911282313630129</v>
       </c>
-      <c r="M10" s="12">
+      <c r="M10" s="11">
         <v>0.94962382237510101</v>
       </c>
     </row>
@@ -4838,10 +4853,10 @@
       <c r="M1" s="1">
         <v>11</v>
       </c>
-      <c r="P1" s="9">
-        <v>0</v>
-      </c>
-      <c r="Q1" s="9">
+      <c r="P1" s="8">
+        <v>0</v>
+      </c>
+      <c r="Q1" s="8">
         <v>7</v>
       </c>
       <c r="R1" s="6" t="s">
@@ -4874,13 +4889,13 @@
       <c r="F2">
         <v>0.90116766699999995</v>
       </c>
-      <c r="G2" s="12">
+      <c r="G2" s="11">
         <v>0.10209418000000001</v>
       </c>
       <c r="H2">
         <v>0.99999999399999995</v>
       </c>
-      <c r="I2" s="12">
+      <c r="I2" s="11">
         <v>1.97554E-3</v>
       </c>
       <c r="J2">
@@ -4892,7 +4907,7 @@
       <c r="L2">
         <v>0.898984279</v>
       </c>
-      <c r="M2" s="10">
+      <c r="M2" s="9">
         <v>0.75799431799999994</v>
       </c>
       <c r="O2" s="3" t="s">
@@ -4941,13 +4956,13 @@
       <c r="G3">
         <v>0.57409199933194033</v>
       </c>
-      <c r="H3" s="12">
+      <c r="H3" s="11">
         <v>3.1977288258686877E-2</v>
       </c>
       <c r="I3">
         <v>0.93178139663832171</v>
       </c>
-      <c r="J3" s="12">
+      <c r="J3" s="11">
         <v>1.4122453821440881E-2</v>
       </c>
       <c r="K3">
@@ -4956,7 +4971,7 @@
       <c r="L3">
         <v>0.86192899489150898</v>
       </c>
-      <c r="M3" s="12">
+      <c r="M3" s="11">
         <v>0.1125428549791273</v>
       </c>
       <c r="O3" s="3" t="s">
@@ -5015,7 +5030,7 @@
       <c r="J4">
         <v>0.99999999406987683</v>
       </c>
-      <c r="K4" s="12">
+      <c r="K4" s="11">
         <v>1.56249973338024E-2</v>
       </c>
       <c r="L4">
@@ -5066,7 +5081,7 @@
         <v>0.99999999540183959</v>
       </c>
       <c r="E5" s="2"/>
-      <c r="F5" s="12">
+      <c r="F5" s="11">
         <v>4.85386120900336E-2</v>
       </c>
       <c r="G5">
@@ -5084,7 +5099,7 @@
       <c r="K5">
         <v>0.94176634311228846</v>
       </c>
-      <c r="L5" s="12">
+      <c r="L5" s="11">
         <v>0</v>
       </c>
       <c r="M5">
@@ -5151,7 +5166,7 @@
       <c r="K6">
         <v>0.94286685456228247</v>
       </c>
-      <c r="L6" s="12">
+      <c r="L6" s="11">
         <v>4.85386120900336E-2</v>
       </c>
       <c r="M6">
@@ -5169,7 +5184,7 @@
         <f>SUM(T2:T5)</f>
         <v>2.1913969591216328E-3</v>
       </c>
-      <c r="U6" s="11">
+      <c r="U6" s="10">
         <f>0.5*(S6+T6)</f>
         <v>1.9755396185357271E-3</v>
       </c>
@@ -5250,7 +5265,7 @@
       <c r="I8">
         <v>0.99999999388987537</v>
       </c>
-      <c r="J8" s="12">
+      <c r="J8" s="11">
         <v>7.8568733577535563E-3</v>
       </c>
       <c r="K8">
@@ -5259,7 +5274,7 @@
       <c r="L8">
         <v>0.99999999673380247</v>
       </c>
-      <c r="M8" s="12">
+      <c r="M8" s="11">
         <v>0.12844187041346949</v>
       </c>
     </row>
@@ -5352,7 +5367,7 @@
       <c r="L10">
         <v>0.94176634311228846</v>
       </c>
-      <c r="M10" s="12">
+      <c r="M10" s="11">
         <v>0.13488801488488661</v>
       </c>
     </row>
@@ -5504,7 +5519,7 @@
       <c r="M13" s="2"/>
     </row>
     <row r="16" spans="1:21" x14ac:dyDescent="0.2">
-      <c r="A16" s="14"/>
+      <c r="A16" s="13"/>
     </row>
     <row r="17" spans="4:4" x14ac:dyDescent="0.2">
       <c r="D17" s="5"/>
